--- a/data/trans_bre/P12_2_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P12_2_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 8,46</t>
+          <t>-5,86; 8,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 13,18</t>
+          <t>-2,91; 12,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 19,22</t>
+          <t>2,62; 18,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 18,31</t>
+          <t>4,69; 18,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 46,84</t>
+          <t>-25,17; 51,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 56,52</t>
+          <t>-8,95; 55,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,61; 86,62</t>
+          <t>8,04; 79,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,79; 99,27</t>
+          <t>17,36; 96,96</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 16,2</t>
+          <t>4,27; 16,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 12,93</t>
+          <t>3,97; 12,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 10,91</t>
+          <t>1,25; 11,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 11,62</t>
+          <t>3,35; 12,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 79,49</t>
+          <t>16,59; 80,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,25; 172,83</t>
+          <t>33,44; 174,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,84; 99,29</t>
+          <t>6,85; 103,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,66; 134,91</t>
+          <t>22,36; 137,57</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 15,25</t>
+          <t>4,19; 15,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 10,92</t>
+          <t>-1,58; 10,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 9,07</t>
+          <t>-2,98; 10,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 6,15</t>
+          <t>-4,04; 6,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,27; 173,19</t>
+          <t>26,67; 169,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 90,2</t>
+          <t>-9,48; 85,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 50,02</t>
+          <t>-12,66; 57,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 47,83</t>
+          <t>-21,2; 45,36</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 19,13</t>
+          <t>7,53; 19,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 26,91</t>
+          <t>13,48; 26,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 13,77</t>
+          <t>0,28; 12,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 5,95</t>
+          <t>-10,75; 5,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,1; 172,5</t>
+          <t>46,41; 170,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,66; 175,66</t>
+          <t>60,46; 170,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 80,14</t>
+          <t>0,84; 73,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,75; 38,9</t>
+          <t>-46,92; 39,14</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 20,21</t>
+          <t>1,86; 20,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,39; 25,77</t>
+          <t>8,76; 25,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 14,37</t>
+          <t>-2,44; 14,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 20,23</t>
+          <t>5,2; 20,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 69,71</t>
+          <t>4,99; 74,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,7; 205,27</t>
+          <t>42,64; 201,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 81,51</t>
+          <t>-10,49; 80,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,78; 61,06</t>
+          <t>12,04; 60,39</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,52; 21,98</t>
+          <t>8,38; 21,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 8,77</t>
+          <t>-3,67; 8,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 11,66</t>
+          <t>-0,35; 11,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 4,07</t>
+          <t>-5,74; 4,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,31; 228,74</t>
+          <t>53,61; 224,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 75,06</t>
+          <t>-21,86; 77,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 120,52</t>
+          <t>-2,27; 125,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 29,7</t>
+          <t>-30,9; 33,56</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,34; 16,87</t>
+          <t>8,5; 16,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,54</t>
+          <t>1,01; 10,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 12,05</t>
+          <t>3,45; 12,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 7,91</t>
+          <t>-12,89; 8,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,52; 194,74</t>
+          <t>68,11; 192,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 57,45</t>
+          <t>4,63; 58,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,86; 81,62</t>
+          <t>18,23; 84,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 41,54</t>
+          <t>-54,86; 44,88</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,32; 13,0</t>
+          <t>3,46; 12,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,37; 10,04</t>
+          <t>2,22; 10,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 9,47</t>
+          <t>3,41; 9,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,27; 16,2</t>
+          <t>6,52; 15,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,37; 48,04</t>
+          <t>10,13; 46,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,51; 64,27</t>
+          <t>11,33; 69,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,75; 150,44</t>
+          <t>38,59; 162,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>52,18; 408,27</t>
+          <t>56,26; 408,51</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,88; 12,2</t>
+          <t>8,19; 12,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,22</t>
+          <t>6,34; 10,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,46</t>
+          <t>4,59; 8,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,17</t>
+          <t>1,97; 9,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37,8; 65,85</t>
+          <t>39,95; 65,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,8; 62,21</t>
+          <t>34,54; 63,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,55; 57,18</t>
+          <t>27,75; 58,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,92; 70,41</t>
+          <t>13,01; 67,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_2_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P12_2_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,59</t>
+          <t>10,73</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 8,06</t>
+          <t>-6,86; 7,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 12,61</t>
+          <t>-4,04; 12,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 18,61</t>
+          <t>1,83; 18,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 18,41</t>
+          <t>4,13; 17,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 51,6</t>
+          <t>-28,46; 42,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 55,69</t>
+          <t>-13,76; 52,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 79,57</t>
+          <t>5,5; 76,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,36; 96,96</t>
+          <t>13,68; 78,05</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,72</t>
+          <t>7,58</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>69,43%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 16,06</t>
+          <t>4,39; 15,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 12,67</t>
+          <t>3,99; 12,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,16</t>
+          <t>1,97; 10,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 12,01</t>
+          <t>3,52; 11,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,59; 80,89</t>
+          <t>16,2; 73,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,44; 174,7</t>
+          <t>32,99; 178,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 103,76</t>
+          <t>13,33; 104,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,36; 137,57</t>
+          <t>25,19; 130,95</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 15,16</t>
+          <t>4,04; 14,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 10,79</t>
+          <t>-0,96; 11,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 10,3</t>
+          <t>-3,13; 9,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 6,04</t>
+          <t>-3,54; 6,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,67; 169,79</t>
+          <t>27,25; 171,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 85,02</t>
+          <t>-5,89; 87,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 57,04</t>
+          <t>-12,62; 52,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 45,36</t>
+          <t>-19,5; 48,13</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,24</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-6,73%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 19,18</t>
+          <t>7,57; 19,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,48; 26,58</t>
+          <t>13,87; 27,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 12,72</t>
+          <t>0,84; 13,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 5,96</t>
+          <t>-2,37; 9,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,41; 170,43</t>
+          <t>45,6; 175,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,46; 170,92</t>
+          <t>63,49; 177,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 73,7</t>
+          <t>2,67; 77,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,92; 39,14</t>
+          <t>-10,83; 72,45</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,16</t>
+          <t>13,71</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 20,61</t>
+          <t>1,11; 20,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,76; 25,05</t>
+          <t>7,96; 25,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 14,21</t>
+          <t>-2,6; 14,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 20,02</t>
+          <t>6,25; 21,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,99; 74,94</t>
+          <t>2,64; 69,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,64; 201,94</t>
+          <t>38,48; 204,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 80,71</t>
+          <t>-9,94; 79,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,04; 60,39</t>
+          <t>15,12; 65,42</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-4,88%</t>
+          <t>-2,13%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,38; 21,23</t>
+          <t>8,76; 21,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 8,55</t>
+          <t>-3,35; 9,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 11,77</t>
+          <t>-0,83; 12,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 4,59</t>
+          <t>-5,37; 4,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53,61; 224,18</t>
+          <t>54,31; 231,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 77,37</t>
+          <t>-19,05; 81,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 125,08</t>
+          <t>-6,46; 122,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 33,56</t>
+          <t>-28,66; 29,87</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>7,64</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,5; 16,79</t>
+          <t>8,49; 16,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,33</t>
+          <t>0,93; 10,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 12,35</t>
+          <t>2,86; 12,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 8,31</t>
+          <t>2,71; 11,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,11; 192,68</t>
+          <t>66,78; 198,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,63; 58,89</t>
+          <t>3,96; 61,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,23; 84,42</t>
+          <t>14,99; 81,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-54,86; 44,88</t>
+          <t>11,88; 69,57</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10,4</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>131,46%</t>
+          <t>70,2%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,46; 12,99</t>
+          <t>3,08; 13,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,22; 10,57</t>
+          <t>2,06; 10,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,41; 9,57</t>
+          <t>3,07; 9,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,52; 15,96</t>
+          <t>4,33; 10,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,13; 46,5</t>
+          <t>9,73; 49,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,33; 69,04</t>
+          <t>10,68; 70,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,59; 162,19</t>
+          <t>36,37; 158,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>56,26; 408,51</t>
+          <t>34,71; 116,99</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>6,62</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,3</t>
+          <t>8,19; 12,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,22</t>
+          <t>6,13; 10,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,48</t>
+          <t>4,64; 8,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 9,01</t>
+          <t>4,71; 8,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>39,95; 65,62</t>
+          <t>40,29; 65,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,54; 63,0</t>
+          <t>33,59; 61,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,75; 58,56</t>
+          <t>27,52; 57,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,01; 67,96</t>
+          <t>26,29; 52,0</t>
         </is>
       </c>
     </row>
